--- a/outputs/374-18.xlsx
+++ b/outputs/374-18.xlsx
@@ -124,16 +124,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -329,62 +333,62 @@
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="2" t="n">
         <v>44400</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>164.74</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="2"/>
+      <c r="H2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D3" s="1" t="n">
+      <c r="D3" s="2" t="n">
         <v>44205.3229166667</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>395.25</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="2"/>
+      <c r="H3" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
